--- a/data/Flass/CL32 - FL-March.xlsx
+++ b/data/Flass/CL32 - FL-March.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ebenezeramoako\NEW\dm_trackers\data\Flass\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3DBACBD1-D5E8-4809-904A-DADB99C99E7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D14F7055-8794-4CAD-80E5-5FF5B487D10B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3435" yWindow="435" windowWidth="15105" windowHeight="15345" xr2:uid="{04EFD3A7-CBBE-4CB1-8442-4E9A4E15E440}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{04EFD3A7-CBBE-4CB1-8442-4E9A4E15E440}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -727,7 +727,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4614E08-7AA5-42E0-964D-A4C08B1AFA30}">
-  <dimension ref="A1:G40"/>
+  <dimension ref="A2:G41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.42578125" customWidth="1"/>
@@ -738,30 +738,13 @@
     <col min="7" max="7" width="11.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="4">
-        <v>46161</v>
-      </c>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-    </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>8</v>
@@ -773,88 +756,88 @@
       <c r="G2" s="5"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="6" t="s">
+      <c r="A3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="6"/>
+      <c r="E3" s="4">
+        <v>46161</v>
+      </c>
       <c r="F3" s="5"/>
       <c r="G3" s="5"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>0</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>16</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="E4" s="6"/>
       <c r="F4" s="5"/>
       <c r="G4" s="5"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="D5" s="6"/>
-      <c r="E5" s="7">
-        <v>46154</v>
+      <c r="D5" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" s="7">
-        <v>46155</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D6" s="6"/>
       <c r="E6" s="7">
-        <v>46161</v>
+        <v>46154</v>
       </c>
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="D7" s="6"/>
+        <v>10</v>
+      </c>
+      <c r="D7" s="7">
+        <v>46155</v>
+      </c>
       <c r="E7" s="7">
         <v>46161</v>
       </c>
@@ -862,45 +845,45 @@
       <c r="G7" s="5"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E8" s="4">
-        <v>46113</v>
+      <c r="A8" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D8" s="6"/>
+      <c r="E8" s="7">
+        <v>46161</v>
       </c>
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="D9" s="6" t="s">
+      <c r="A9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E9" s="6"/>
+      <c r="E9" s="4">
+        <v>46113</v>
+      </c>
       <c r="F9" s="5"/>
       <c r="G9" s="5"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>0</v>
@@ -914,10 +897,10 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>0</v>
@@ -931,10 +914,10 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>0</v>
@@ -948,10 +931,10 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>0</v>
@@ -965,10 +948,10 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>0</v>
@@ -982,10 +965,10 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>0</v>
@@ -999,16 +982,16 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="D16" s="7">
-        <v>46113</v>
+      <c r="D16" s="6" t="s">
+        <v>8</v>
       </c>
       <c r="E16" s="6"/>
       <c r="F16" s="5"/>
@@ -1016,10 +999,10 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>0</v>
@@ -1032,64 +1015,62 @@
       <c r="G17" s="5"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E18" s="4">
-        <v>46119</v>
-      </c>
+      <c r="A18" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D18" s="7">
+        <v>46113</v>
+      </c>
+      <c r="E18" s="6"/>
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="D19" s="6" t="s">
+      <c r="A19" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E19" s="6"/>
+      <c r="E19" s="4">
+        <v>46119</v>
+      </c>
       <c r="F19" s="5"/>
       <c r="G19" s="5"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>0</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>46</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="E20" s="6"/>
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>0</v>
@@ -1103,54 +1084,54 @@
       <c r="F21" s="5"/>
       <c r="G21" s="5"/>
     </row>
-    <row r="22" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>50</v>
+        <v>47</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>48</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="D22" s="6"/>
+      <c r="D22" s="6" t="s">
+        <v>45</v>
+      </c>
       <c r="E22" s="6" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="F22" s="5"/>
       <c r="G22" s="5"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>53</v>
+        <v>49</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>50</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="D23" s="6" t="s">
+      <c r="D23" s="6"/>
+      <c r="E23" s="6" t="s">
         <v>51</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>54</v>
       </c>
       <c r="F23" s="5"/>
       <c r="G23" s="5"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>0</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>54</v>
@@ -1160,273 +1141,273 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="E25" s="7">
-        <v>46119</v>
+        <v>57</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>54</v>
       </c>
       <c r="F25" s="5"/>
       <c r="G25" s="5"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D26" s="4">
-        <v>46120</v>
-      </c>
-      <c r="E26" s="4">
-        <v>46157</v>
+      <c r="A26" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="E26" s="7">
+        <v>46119</v>
       </c>
       <c r="F26" s="5"/>
       <c r="G26" s="5"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D27" s="4">
         <v>46120</v>
       </c>
       <c r="E27" s="4">
-        <v>46140</v>
+        <v>46157</v>
       </c>
       <c r="F27" s="5"/>
       <c r="G27" s="5"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D28" s="7">
+      <c r="A28" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D28" s="4">
         <v>46120</v>
       </c>
-      <c r="E28" s="7">
-        <v>46126</v>
+      <c r="E28" s="4">
+        <v>46140</v>
       </c>
       <c r="F28" s="5"/>
       <c r="G28" s="5"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D29" s="7">
-        <v>46127</v>
+        <v>46120</v>
       </c>
       <c r="E29" s="7">
-        <v>46129</v>
+        <v>46126</v>
       </c>
       <c r="F29" s="5"/>
       <c r="G29" s="5"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D30" s="7">
-        <v>46132</v>
+        <v>46127</v>
       </c>
       <c r="E30" s="7">
-        <v>46136</v>
+        <v>46129</v>
       </c>
       <c r="F30" s="5"/>
       <c r="G30" s="5"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D31" s="7">
-        <v>46139</v>
+        <v>46132</v>
       </c>
       <c r="E31" s="7">
-        <v>46140</v>
+        <v>46136</v>
       </c>
       <c r="F31" s="5"/>
       <c r="G31" s="5"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B32" s="2"/>
-      <c r="C32" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D32" s="4">
-        <v>46120</v>
-      </c>
-      <c r="E32" s="4">
-        <v>46157</v>
+      <c r="A32" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D32" s="7">
+        <v>46139</v>
+      </c>
+      <c r="E32" s="7">
+        <v>46140</v>
       </c>
       <c r="F32" s="5"/>
       <c r="G32" s="5"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D33" s="7">
+      <c r="A33" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D33" s="4">
         <v>46120</v>
       </c>
-      <c r="E33" s="7">
-        <v>46121</v>
+      <c r="E33" s="4">
+        <v>46157</v>
       </c>
       <c r="F33" s="5"/>
       <c r="G33" s="5"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D34" s="7">
-        <v>46132</v>
+        <v>46120</v>
       </c>
       <c r="E34" s="7">
-        <v>46136</v>
+        <v>46121</v>
       </c>
       <c r="F34" s="5"/>
       <c r="G34" s="5"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>10</v>
       </c>
       <c r="D35" s="7">
-        <v>46139</v>
+        <v>46132</v>
       </c>
       <c r="E35" s="7">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="F35" s="5"/>
       <c r="G35" s="5"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C36" s="5" t="s">
         <v>10</v>
       </c>
       <c r="D36" s="7">
-        <v>46147</v>
+        <v>46139</v>
       </c>
       <c r="E36" s="7">
-        <v>46153</v>
+        <v>46143</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="5"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C37" s="5" t="s">
         <v>10</v>
       </c>
       <c r="D37" s="7">
+        <v>46147</v>
+      </c>
+      <c r="E37" s="7">
         <v>46153</v>
-      </c>
-      <c r="E37" s="7">
-        <v>46157</v>
       </c>
       <c r="F37" s="5"/>
       <c r="G37" s="5"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D38" s="7">
-        <v>46154</v>
+        <v>46153</v>
       </c>
       <c r="E38" s="7">
-        <v>46154</v>
+        <v>46157</v>
       </c>
       <c r="F38" s="5"/>
       <c r="G38" s="5"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D39" s="7">
         <v>46154</v>
@@ -1439,20 +1420,39 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="D40" s="6"/>
+        <v>3</v>
+      </c>
+      <c r="D40" s="7">
+        <v>46154</v>
+      </c>
       <c r="E40" s="7">
-        <v>46157</v>
+        <v>46154</v>
       </c>
       <c r="F40" s="5"/>
       <c r="G40" s="5"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D41" s="6"/>
+      <c r="E41" s="7">
+        <v>46157</v>
+      </c>
+      <c r="F41" s="5"/>
+      <c r="G41" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/Flass/CL32 - FL-March.xlsx
+++ b/data/Flass/CL32 - FL-March.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ebenezeramoako\NEW\dm_trackers\data\Flass\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{780F1A0A-70C7-453A-BFA5-A4DCF6C85977}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15AFF105-C8BE-4DBD-B2CB-C4DCFEC0837D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="689" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="682" uniqueCount="219">
   <si>
     <t>Activity ID</t>
   </si>
@@ -41,9 +41,6 @@
     <t>Activity Name</t>
   </si>
   <si>
-    <t>Remaining Duration(h)</t>
-  </si>
-  <si>
     <t>Primary Constraint</t>
   </si>
   <si>
@@ -78,12 +75,6 @@
   </si>
   <si>
     <t>Planned Completion</t>
-  </si>
-  <si>
-    <t>AR-FL-KD-1010</t>
-  </si>
-  <si>
-    <t>Team Mobilisation</t>
   </si>
   <si>
     <t>100</t>
@@ -693,16 +684,22 @@
     <t>BL Finish</t>
   </si>
   <si>
-    <t>Variance - BL Project Finish Date(h)</t>
-  </si>
-  <si>
-    <t>Total Float(h)</t>
+    <t>Remaining Duration</t>
+  </si>
+  <si>
+    <t>Variance - BL Project Finish Date</t>
+  </si>
+  <si>
+    <t>Total Float</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+  </numFmts>
   <fonts count="1">
     <font>
       <sz val="11"/>
@@ -729,13 +726,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1072,7 +1072,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K97"/>
+  <dimension ref="A1:K96"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="54" customWidth="1"/>
@@ -1091,136 +1091,136 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="J1" t="s">
+        <v>218</v>
+      </c>
+      <c r="K1" t="s">
         <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="J1" t="s">
-        <v>220</v>
-      </c>
-      <c r="K1" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
       <c r="C2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="4">
+        <v>46171.708333333299</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="4">
+        <v>46161.708333333299</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="3">
-        <v>46171.708333333299</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H2" s="3">
-        <v>46161.708333333299</v>
-      </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" t="s">
         <v>8</v>
       </c>
-      <c r="J2" t="s">
-        <v>9</v>
-      </c>
       <c r="K2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="3">
+      <c r="D3" s="4">
         <v>46164.333333333299</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="4">
         <v>46171.708333333299</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G3" s="3">
+        <v>5</v>
+      </c>
+      <c r="G3" s="4">
         <v>46155.333333333299</v>
       </c>
-      <c r="H3" s="3">
+      <c r="H3" s="4">
         <v>46161.708333333299</v>
       </c>
       <c r="I3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J3" t="s">
         <v>8</v>
       </c>
-      <c r="J3" t="s">
-        <v>9</v>
-      </c>
       <c r="K3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
         <v>13</v>
       </c>
-      <c r="B4" t="s">
-        <v>14</v>
-      </c>
       <c r="C4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="4">
+        <v>46163.708333333299</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H4" s="4">
+        <v>46154.708333333299</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="3">
-        <v>46163.708333333299</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H4" s="3">
-        <v>46154.708333333299</v>
-      </c>
-      <c r="I4" s="2" t="s">
+      <c r="J4" t="s">
         <v>8</v>
       </c>
-      <c r="J4" t="s">
-        <v>9</v>
-      </c>
       <c r="K4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1231,31 +1231,31 @@
         <v>16</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="3">
-        <v>46084.333333333299</v>
-      </c>
-      <c r="E5" s="3">
-        <v>46087.708333333299</v>
+        <v>5</v>
+      </c>
+      <c r="D5" s="4">
+        <v>46121.333333333299</v>
+      </c>
+      <c r="E5" s="4">
+        <v>46129.708333333299</v>
       </c>
       <c r="F5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="4">
+        <v>46107.333333333299</v>
+      </c>
+      <c r="H5" s="4">
+        <v>46119.708333333299</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="G5" s="3">
-        <v>46084.333333333299</v>
-      </c>
-      <c r="H5" s="3">
-        <v>46087.708333333299</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="J5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1266,241 +1266,241 @@
         <v>19</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" s="3">
-        <v>46121.333333333299</v>
-      </c>
-      <c r="E6" s="3">
-        <v>46129.708333333299</v>
+        <v>5</v>
+      </c>
+      <c r="D6" s="4">
+        <v>46100.333333333299</v>
+      </c>
+      <c r="E6" s="4">
+        <v>46106.708333333299</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G6" s="3">
-        <v>46107.333333333299</v>
-      </c>
-      <c r="H6" s="3">
-        <v>46119.708333333299</v>
+        <v>14</v>
+      </c>
+      <c r="G6" s="4">
+        <v>46100.333333333299</v>
+      </c>
+      <c r="H6" s="4">
+        <v>46106.708333333299</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="J6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" t="s">
         <v>21</v>
       </c>
-      <c r="B7" t="s">
-        <v>22</v>
-      </c>
       <c r="C7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D7" s="3">
-        <v>46100.333333333299</v>
-      </c>
-      <c r="E7" s="3">
+        <v>5</v>
+      </c>
+      <c r="D7" s="4">
+        <v>46097.333333333299</v>
+      </c>
+      <c r="E7" s="4">
         <v>46106.708333333299</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G7" s="3">
-        <v>46100.333333333299</v>
-      </c>
-      <c r="H7" s="3">
+        <v>14</v>
+      </c>
+      <c r="G7" s="4">
+        <v>46097.333333333299</v>
+      </c>
+      <c r="H7" s="4">
         <v>46106.708333333299</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" t="s">
         <v>23</v>
       </c>
-      <c r="B8" t="s">
-        <v>24</v>
-      </c>
       <c r="C8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D8" s="3">
+        <v>5</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" s="4">
         <v>46097.333333333299</v>
       </c>
-      <c r="E8" s="3">
-        <v>46106.708333333299</v>
-      </c>
       <c r="F8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G8" s="3">
+        <v>14</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H8" s="4">
         <v>46097.333333333299</v>
       </c>
-      <c r="H8" s="3">
-        <v>46106.708333333299</v>
-      </c>
       <c r="I8" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" t="s">
         <v>25</v>
       </c>
-      <c r="B9" t="s">
-        <v>26</v>
-      </c>
       <c r="C9" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E9" s="3">
-        <v>46097.333333333299</v>
+        <v>5</v>
+      </c>
+      <c r="D9" s="4">
+        <v>46090.333333333299</v>
+      </c>
+      <c r="E9" s="4">
+        <v>46094.708333333299</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H9" s="3">
-        <v>46097.333333333299</v>
+        <v>14</v>
+      </c>
+      <c r="G9" s="4">
+        <v>46090.333333333299</v>
+      </c>
+      <c r="H9" s="4">
+        <v>46094.708333333299</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" t="s">
         <v>27</v>
       </c>
-      <c r="B10" t="s">
-        <v>28</v>
-      </c>
       <c r="C10" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D10" s="3">
+        <v>5</v>
+      </c>
+      <c r="D10" s="4">
         <v>46090.333333333299</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E10" s="4">
         <v>46094.708333333299</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G10" s="3">
+        <v>14</v>
+      </c>
+      <c r="G10" s="4">
         <v>46090.333333333299</v>
       </c>
-      <c r="H10" s="3">
+      <c r="H10" s="4">
         <v>46094.708333333299</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J10" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K10" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" t="s">
         <v>29</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D11" s="3">
-        <v>46090.333333333299</v>
-      </c>
-      <c r="E11" s="3">
-        <v>46094.708333333299</v>
+      <c r="D11" s="4">
+        <v>46174.333333333299</v>
+      </c>
+      <c r="E11" s="4">
+        <v>46175.708333333299</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G11" s="3">
-        <v>46090.333333333299</v>
-      </c>
-      <c r="H11" s="3">
-        <v>46094.708333333299</v>
+        <v>5</v>
+      </c>
+      <c r="G11" s="4">
+        <v>46139.333333333299</v>
+      </c>
+      <c r="H11" s="4">
+        <v>46140.708333333299</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="J11" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="K11" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D12" s="4">
+        <v>46141.333333333299</v>
+      </c>
+      <c r="E12" s="4">
+        <v>46171.708333333299</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G12" s="4">
+        <v>46132.333333333299</v>
+      </c>
+      <c r="H12" s="4">
+        <v>46136.708333333299</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B12" t="s">
+      <c r="J12" t="s">
         <v>32</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D12" s="3">
-        <v>46174.333333333299</v>
-      </c>
-      <c r="E12" s="3">
-        <v>46175.708333333299</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G12" s="3">
-        <v>46139.333333333299</v>
-      </c>
-      <c r="H12" s="3">
-        <v>46140.708333333299</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="J12" t="s">
-        <v>35</v>
-      </c>
       <c r="K12" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1511,66 +1511,66 @@
         <v>37</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D13" s="3">
-        <v>46141.333333333299</v>
-      </c>
-      <c r="E13" s="3">
-        <v>46171.708333333299</v>
+        <v>5</v>
+      </c>
+      <c r="D13" s="4">
+        <v>46136.333333333299</v>
+      </c>
+      <c r="E13" s="4">
+        <v>46140.708333333299</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G13" s="3">
-        <v>46132.333333333299</v>
-      </c>
-      <c r="H13" s="3">
-        <v>46136.708333333299</v>
+        <v>14</v>
+      </c>
+      <c r="G13" s="4">
+        <v>46127.333333333299</v>
+      </c>
+      <c r="H13" s="4">
+        <v>46129.708333333299</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="J13" t="s">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="K13" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" t="s">
         <v>39</v>
       </c>
-      <c r="B14" t="s">
-        <v>40</v>
-      </c>
       <c r="C14" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D14" s="3">
-        <v>46136.333333333299</v>
-      </c>
-      <c r="E14" s="3">
-        <v>46140.708333333299</v>
+        <v>5</v>
+      </c>
+      <c r="D14" s="4">
+        <v>46129.333333333299</v>
+      </c>
+      <c r="E14" s="4">
+        <v>46135.708333333299</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G14" s="3">
-        <v>46127.333333333299</v>
-      </c>
-      <c r="H14" s="3">
-        <v>46129.708333333299</v>
+        <v>14</v>
+      </c>
+      <c r="G14" s="4">
+        <v>46120.333333333299</v>
+      </c>
+      <c r="H14" s="4">
+        <v>46126.708333333299</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J14" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K14" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1581,31 +1581,31 @@
         <v>42</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D15" s="3">
-        <v>46129.333333333299</v>
-      </c>
-      <c r="E15" s="3">
-        <v>46135.708333333299</v>
+        <v>43</v>
+      </c>
+      <c r="D15" s="4">
+        <v>46163.333333333299</v>
+      </c>
+      <c r="E15" s="4">
+        <v>46163.708333333299</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G15" s="3">
-        <v>46120.333333333299</v>
-      </c>
-      <c r="H15" s="3">
-        <v>46126.708333333299</v>
+        <v>5</v>
+      </c>
+      <c r="G15" s="4">
+        <v>46154.333333333299</v>
+      </c>
+      <c r="H15" s="4">
+        <v>46154.708333333299</v>
       </c>
       <c r="I15" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J15" t="s">
         <v>8</v>
       </c>
-      <c r="J15" t="s">
-        <v>7</v>
-      </c>
       <c r="K15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1616,136 +1616,136 @@
         <v>45</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D16" s="3">
-        <v>46163.333333333299</v>
-      </c>
-      <c r="E16" s="3">
-        <v>46163.708333333299</v>
+        <v>11</v>
+      </c>
+      <c r="D16" s="4">
+        <v>46162.333333333299</v>
+      </c>
+      <c r="E16" s="4">
+        <v>46169.708333333299</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G16" s="3">
-        <v>46154.333333333299</v>
-      </c>
-      <c r="H16" s="3">
-        <v>46154.708333333299</v>
+        <v>5</v>
+      </c>
+      <c r="G16" s="4">
+        <v>46153.333333333299</v>
+      </c>
+      <c r="H16" s="4">
+        <v>46157.708333333299</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J16" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="K16" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
+        <v>46</v>
+      </c>
+      <c r="B17" t="s">
         <v>47</v>
       </c>
-      <c r="B17" t="s">
-        <v>48</v>
-      </c>
       <c r="C17" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D17" s="3">
-        <v>46162.333333333299</v>
-      </c>
-      <c r="E17" s="3">
-        <v>46169.708333333299</v>
+        <v>11</v>
+      </c>
+      <c r="D17" s="4">
+        <v>46156.333333333299</v>
+      </c>
+      <c r="E17" s="4">
+        <v>46162.708333333299</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G17" s="3">
-        <v>46153.333333333299</v>
-      </c>
-      <c r="H17" s="3">
-        <v>46157.708333333299</v>
+        <v>5</v>
+      </c>
+      <c r="G17" s="4">
+        <v>46147.333333333299</v>
+      </c>
+      <c r="H17" s="4">
+        <v>46153.708333333299</v>
       </c>
       <c r="I17" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J17" t="s">
         <v>8</v>
       </c>
-      <c r="J17" t="s">
-        <v>43</v>
-      </c>
       <c r="K17" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
+        <v>48</v>
+      </c>
+      <c r="B18" t="s">
         <v>49</v>
       </c>
-      <c r="B18" t="s">
-        <v>50</v>
-      </c>
       <c r="C18" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D18" s="3">
-        <v>46156.333333333299</v>
-      </c>
-      <c r="E18" s="3">
-        <v>46162.708333333299</v>
+        <v>11</v>
+      </c>
+      <c r="D18" s="4">
+        <v>46149.333333333299</v>
+      </c>
+      <c r="E18" s="4">
+        <v>46155.708333333299</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G18" s="3">
-        <v>46147.333333333299</v>
-      </c>
-      <c r="H18" s="3">
-        <v>46153.708333333299</v>
+        <v>5</v>
+      </c>
+      <c r="G18" s="4">
+        <v>46139.333333333299</v>
+      </c>
+      <c r="H18" s="4">
+        <v>46143.708333333299</v>
       </c>
       <c r="I18" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J18" t="s">
         <v>8</v>
       </c>
-      <c r="J18" t="s">
-        <v>9</v>
-      </c>
       <c r="K18" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:11">
       <c r="A19" t="s">
+        <v>50</v>
+      </c>
+      <c r="B19" t="s">
         <v>51</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D19" s="4">
+        <v>46141.333333333299</v>
+      </c>
+      <c r="E19" s="4">
+        <v>46148.708333333299</v>
+      </c>
+      <c r="F19" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D19" s="3">
-        <v>46149.333333333299</v>
-      </c>
-      <c r="E19" s="3">
-        <v>46155.708333333299</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G19" s="3">
-        <v>46139.333333333299</v>
-      </c>
-      <c r="H19" s="3">
-        <v>46143.708333333299</v>
+      <c r="G19" s="4">
+        <v>46132.333333333299</v>
+      </c>
+      <c r="H19" s="4">
+        <v>46136.708333333299</v>
       </c>
       <c r="I19" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J19" t="s">
         <v>8</v>
       </c>
-      <c r="J19" t="s">
-        <v>9</v>
-      </c>
       <c r="K19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -1756,66 +1756,66 @@
         <v>54</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D20" s="3">
-        <v>46141.333333333299</v>
-      </c>
-      <c r="E20" s="3">
-        <v>46148.708333333299</v>
+        <v>5</v>
+      </c>
+      <c r="D20" s="4">
+        <v>46129.333333333299</v>
+      </c>
+      <c r="E20" s="4">
+        <v>46132.708333333299</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="G20" s="3">
-        <v>46132.333333333299</v>
-      </c>
-      <c r="H20" s="3">
-        <v>46136.708333333299</v>
+        <v>14</v>
+      </c>
+      <c r="G20" s="4">
+        <v>46120.333333333299</v>
+      </c>
+      <c r="H20" s="4">
+        <v>46121.708333333299</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J20" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K20" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:11">
       <c r="A21" t="s">
+        <v>55</v>
+      </c>
+      <c r="B21" t="s">
         <v>56</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D21" s="4">
+        <v>45947.333333333299</v>
+      </c>
+      <c r="E21" s="4">
+        <v>45953.708333333299</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G21" s="4">
+        <v>45947.333333333299</v>
+      </c>
+      <c r="H21" s="4">
+        <v>45953.708333333299</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J21" t="s">
+        <v>6</v>
+      </c>
+      <c r="K21" t="s">
         <v>57</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D21" s="3">
-        <v>46129.333333333299</v>
-      </c>
-      <c r="E21" s="3">
-        <v>46132.708333333299</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G21" s="3">
-        <v>46120.333333333299</v>
-      </c>
-      <c r="H21" s="3">
-        <v>46121.708333333299</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J21" t="s">
-        <v>7</v>
-      </c>
-      <c r="K21" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -1826,1081 +1826,1081 @@
         <v>59</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D22" s="3">
-        <v>45947.333333333299</v>
-      </c>
-      <c r="E22" s="3">
-        <v>45953.708333333299</v>
+        <v>5</v>
+      </c>
+      <c r="D22" s="4">
+        <v>45940.333333333299</v>
+      </c>
+      <c r="E22" s="4">
+        <v>45946.708333333299</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G22" s="3">
-        <v>45947.333333333299</v>
-      </c>
-      <c r="H22" s="3">
-        <v>45953.708333333299</v>
+        <v>14</v>
+      </c>
+      <c r="G22" s="4">
+        <v>45940.333333333299</v>
+      </c>
+      <c r="H22" s="4">
+        <v>45946.708333333299</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J22" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K22" t="s">
-        <v>60</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" spans="1:11">
       <c r="A23" t="s">
+        <v>60</v>
+      </c>
+      <c r="B23" t="s">
         <v>61</v>
       </c>
-      <c r="B23" t="s">
-        <v>62</v>
-      </c>
       <c r="C23" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D23" s="3">
-        <v>45940.333333333299</v>
-      </c>
-      <c r="E23" s="3">
-        <v>45946.708333333299</v>
+        <v>5</v>
+      </c>
+      <c r="D23" s="4">
+        <v>45919.333333333299</v>
+      </c>
+      <c r="E23" s="4">
+        <v>45932.708333333299</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G23" s="3">
-        <v>45940.333333333299</v>
-      </c>
-      <c r="H23" s="3">
-        <v>45946.708333333299</v>
+        <v>14</v>
+      </c>
+      <c r="G23" s="4">
+        <v>45919.333333333299</v>
+      </c>
+      <c r="H23" s="4">
+        <v>45932.708333333299</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J23" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K23" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:11">
       <c r="A24" t="s">
+        <v>62</v>
+      </c>
+      <c r="B24" t="s">
         <v>63</v>
       </c>
-      <c r="B24" t="s">
-        <v>64</v>
-      </c>
       <c r="C24" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D24" s="3">
+        <v>5</v>
+      </c>
+      <c r="D24" s="4">
         <v>45919.333333333299</v>
       </c>
-      <c r="E24" s="3">
-        <v>45932.708333333299</v>
+      <c r="E24" s="4">
+        <v>45960.708333333299</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G24" s="3">
+        <v>14</v>
+      </c>
+      <c r="G24" s="4">
         <v>45919.333333333299</v>
       </c>
-      <c r="H24" s="3">
-        <v>45932.708333333299</v>
+      <c r="H24" s="4">
+        <v>45960.708333333299</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J24" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K24" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:11">
       <c r="A25" t="s">
+        <v>64</v>
+      </c>
+      <c r="B25" t="s">
         <v>65</v>
       </c>
-      <c r="B25" t="s">
-        <v>66</v>
-      </c>
       <c r="C25" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D25" s="3">
+        <v>5</v>
+      </c>
+      <c r="D25" s="4">
         <v>45919.333333333299</v>
       </c>
-      <c r="E25" s="3">
-        <v>45960.708333333299</v>
+      <c r="E25" s="4">
+        <v>45954.708333333299</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G25" s="3">
+        <v>14</v>
+      </c>
+      <c r="G25" s="4">
         <v>45919.333333333299</v>
       </c>
-      <c r="H25" s="3">
-        <v>45960.708333333299</v>
+      <c r="H25" s="4">
+        <v>45954.708333333299</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J25" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K25" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:11">
       <c r="A26" t="s">
+        <v>66</v>
+      </c>
+      <c r="B26" t="s">
         <v>67</v>
       </c>
-      <c r="B26" t="s">
-        <v>68</v>
-      </c>
       <c r="C26" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D26" s="3">
-        <v>45919.333333333299</v>
-      </c>
-      <c r="E26" s="3">
-        <v>45954.708333333299</v>
+        <v>5</v>
+      </c>
+      <c r="D26" s="4">
+        <v>45981.333333333299</v>
+      </c>
+      <c r="E26" s="4">
+        <v>45999.708333333299</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G26" s="3">
-        <v>45919.333333333299</v>
-      </c>
-      <c r="H26" s="3">
-        <v>45954.708333333299</v>
+        <v>14</v>
+      </c>
+      <c r="G26" s="4">
+        <v>45981.333333333299</v>
+      </c>
+      <c r="H26" s="4">
+        <v>45999.708333333299</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J26" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K26" t="s">
-        <v>7</v>
+        <v>57</v>
       </c>
     </row>
     <row r="27" spans="1:11">
       <c r="A27" t="s">
+        <v>68</v>
+      </c>
+      <c r="B27" t="s">
         <v>69</v>
       </c>
-      <c r="B27" t="s">
-        <v>70</v>
-      </c>
       <c r="C27" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D27" s="3">
-        <v>45981.333333333299</v>
-      </c>
-      <c r="E27" s="3">
-        <v>45999.708333333299</v>
+        <v>5</v>
+      </c>
+      <c r="D27" s="4">
+        <v>45919.333333333299</v>
+      </c>
+      <c r="E27" s="4">
+        <v>45975.708333333299</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G27" s="3">
-        <v>45981.333333333299</v>
-      </c>
-      <c r="H27" s="3">
-        <v>45999.708333333299</v>
+        <v>14</v>
+      </c>
+      <c r="G27" s="4">
+        <v>45919.333333333299</v>
+      </c>
+      <c r="H27" s="4">
+        <v>45975.708333333299</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J27" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K27" t="s">
-        <v>60</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:11">
       <c r="A28" t="s">
+        <v>70</v>
+      </c>
+      <c r="B28" t="s">
         <v>71</v>
       </c>
-      <c r="B28" t="s">
-        <v>72</v>
-      </c>
       <c r="C28" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D28" s="3">
+        <v>5</v>
+      </c>
+      <c r="D28" s="4">
         <v>45919.333333333299</v>
       </c>
-      <c r="E28" s="3">
-        <v>45975.708333333299</v>
+      <c r="E28" s="4">
+        <v>45936.708333333299</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G28" s="3">
+        <v>14</v>
+      </c>
+      <c r="G28" s="4">
         <v>45919.333333333299</v>
       </c>
-      <c r="H28" s="3">
-        <v>45975.708333333299</v>
+      <c r="H28" s="4">
+        <v>45936.708333333299</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J28" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K28" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:11">
       <c r="A29" t="s">
+        <v>72</v>
+      </c>
+      <c r="B29" t="s">
         <v>73</v>
       </c>
-      <c r="B29" t="s">
-        <v>74</v>
-      </c>
       <c r="C29" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D29" s="3">
-        <v>45919.333333333299</v>
-      </c>
-      <c r="E29" s="3">
-        <v>45936.708333333299</v>
+        <v>5</v>
+      </c>
+      <c r="D29" s="4">
+        <v>45905.333333333299</v>
+      </c>
+      <c r="E29" s="4">
+        <v>45918.708333333299</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G29" s="3">
-        <v>45919.333333333299</v>
-      </c>
-      <c r="H29" s="3">
-        <v>45936.708333333299</v>
+        <v>14</v>
+      </c>
+      <c r="G29" s="4">
+        <v>45905.333333333299</v>
+      </c>
+      <c r="H29" s="4">
+        <v>45918.708333333299</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J29" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K29" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:11">
       <c r="A30" t="s">
+        <v>74</v>
+      </c>
+      <c r="B30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D30" s="4">
+        <v>46192.333333333299</v>
+      </c>
+      <c r="E30" s="4">
+        <v>46192.333333333299</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G30" s="4">
+        <v>46171.333333333299</v>
+      </c>
+      <c r="H30" s="4">
+        <v>46171.333333333299</v>
+      </c>
+      <c r="I30" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B30" t="s">
-        <v>76</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D30" s="3">
-        <v>45905.333333333299</v>
-      </c>
-      <c r="E30" s="3">
-        <v>45918.708333333299</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G30" s="3">
-        <v>45905.333333333299</v>
-      </c>
-      <c r="H30" s="3">
-        <v>45918.708333333299</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="J30" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K30" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" spans="1:11">
       <c r="A31" t="s">
+        <v>76</v>
+      </c>
+      <c r="B31" t="s">
         <v>77</v>
       </c>
-      <c r="B31" t="s">
-        <v>11</v>
-      </c>
       <c r="C31" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D31" s="3">
-        <v>46192.333333333299</v>
-      </c>
-      <c r="E31" s="3">
-        <v>46192.333333333299</v>
+        <v>5</v>
+      </c>
+      <c r="D31" s="4">
+        <v>45950.333333333299</v>
+      </c>
+      <c r="E31" s="4">
+        <v>45953.708333333299</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G31" s="3">
-        <v>46171.333333333299</v>
-      </c>
-      <c r="H31" s="3">
-        <v>46171.333333333299</v>
+        <v>14</v>
+      </c>
+      <c r="G31" s="4">
+        <v>45950.333333333299</v>
+      </c>
+      <c r="H31" s="4">
+        <v>45953.708333333299</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>78</v>
+        <v>5</v>
       </c>
       <c r="J31" t="s">
         <v>6</v>
       </c>
       <c r="K31" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32" spans="1:11">
       <c r="A32" t="s">
+        <v>78</v>
+      </c>
+      <c r="B32" t="s">
         <v>79</v>
       </c>
-      <c r="B32" t="s">
-        <v>80</v>
-      </c>
       <c r="C32" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D32" s="3">
-        <v>45950.333333333299</v>
-      </c>
-      <c r="E32" s="3">
-        <v>45953.708333333299</v>
+        <v>5</v>
+      </c>
+      <c r="D32" s="4">
+        <v>45933.333333333299</v>
+      </c>
+      <c r="E32" s="4">
+        <v>45947.708333333299</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G32" s="3">
-        <v>45950.333333333299</v>
-      </c>
-      <c r="H32" s="3">
-        <v>45953.708333333299</v>
+        <v>14</v>
+      </c>
+      <c r="G32" s="4">
+        <v>45933.333333333299</v>
+      </c>
+      <c r="H32" s="4">
+        <v>45947.708333333299</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J32" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K32" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33" spans="1:11">
       <c r="A33" t="s">
+        <v>80</v>
+      </c>
+      <c r="B33" t="s">
         <v>81</v>
       </c>
-      <c r="B33" t="s">
-        <v>82</v>
-      </c>
       <c r="C33" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D33" s="3">
-        <v>45933.333333333299</v>
-      </c>
-      <c r="E33" s="3">
+        <v>5</v>
+      </c>
+      <c r="D33" s="4">
+        <v>45919.333333333299</v>
+      </c>
+      <c r="E33" s="4">
         <v>45947.708333333299</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G33" s="3">
-        <v>45933.333333333299</v>
-      </c>
-      <c r="H33" s="3">
+        <v>14</v>
+      </c>
+      <c r="G33" s="4">
+        <v>45919.333333333299</v>
+      </c>
+      <c r="H33" s="4">
         <v>45947.708333333299</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J33" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K33" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:11">
       <c r="A34" t="s">
+        <v>82</v>
+      </c>
+      <c r="B34" t="s">
         <v>83</v>
       </c>
-      <c r="B34" t="s">
-        <v>84</v>
-      </c>
       <c r="C34" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D34" s="3">
+        <v>5</v>
+      </c>
+      <c r="D34" s="4">
         <v>45919.333333333299</v>
       </c>
-      <c r="E34" s="3">
+      <c r="E34" s="4">
         <v>45947.708333333299</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G34" s="3">
+        <v>14</v>
+      </c>
+      <c r="G34" s="4">
         <v>45919.333333333299</v>
       </c>
-      <c r="H34" s="3">
+      <c r="H34" s="4">
         <v>45947.708333333299</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J34" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K34" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35" spans="1:11">
       <c r="A35" t="s">
+        <v>84</v>
+      </c>
+      <c r="B35" t="s">
         <v>85</v>
       </c>
-      <c r="B35" t="s">
-        <v>86</v>
-      </c>
       <c r="C35" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D35" s="3">
-        <v>45919.333333333299</v>
-      </c>
-      <c r="E35" s="3">
-        <v>45947.708333333299</v>
+        <v>5</v>
+      </c>
+      <c r="D35" s="4">
+        <v>45957.708333333299</v>
+      </c>
+      <c r="E35" s="4">
+        <v>46010.708333333299</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G35" s="3">
-        <v>45919.333333333299</v>
-      </c>
-      <c r="H35" s="3">
-        <v>45947.708333333299</v>
+        <v>14</v>
+      </c>
+      <c r="G35" s="4">
+        <v>45957.708333333299</v>
+      </c>
+      <c r="H35" s="4">
+        <v>46010.708333333299</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J35" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K35" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36" spans="1:11">
       <c r="A36" t="s">
+        <v>86</v>
+      </c>
+      <c r="B36" t="s">
         <v>87</v>
       </c>
-      <c r="B36" t="s">
-        <v>88</v>
-      </c>
       <c r="C36" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D36" s="3">
-        <v>45957.708333333299</v>
-      </c>
-      <c r="E36" s="3">
-        <v>46010.708333333299</v>
+        <v>5</v>
+      </c>
+      <c r="D36" s="4">
+        <v>45965.333333333299</v>
+      </c>
+      <c r="E36" s="4">
+        <v>45974.708333333299</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G36" s="3">
-        <v>45957.708333333299</v>
-      </c>
-      <c r="H36" s="3">
-        <v>46010.708333333299</v>
+        <v>14</v>
+      </c>
+      <c r="G36" s="4">
+        <v>45965.333333333299</v>
+      </c>
+      <c r="H36" s="4">
+        <v>45974.708333333299</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J36" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K36" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37" spans="1:11">
       <c r="A37" t="s">
+        <v>88</v>
+      </c>
+      <c r="B37" t="s">
         <v>89</v>
       </c>
-      <c r="B37" t="s">
-        <v>90</v>
-      </c>
       <c r="C37" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D37" s="3">
-        <v>45965.333333333299</v>
-      </c>
-      <c r="E37" s="3">
-        <v>45974.708333333299</v>
+        <v>5</v>
+      </c>
+      <c r="D37" s="4">
+        <v>45958.333333333299</v>
+      </c>
+      <c r="E37" s="4">
+        <v>45960.708333333299</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G37" s="3">
-        <v>45965.333333333299</v>
-      </c>
-      <c r="H37" s="3">
-        <v>45974.708333333299</v>
+        <v>14</v>
+      </c>
+      <c r="G37" s="4">
+        <v>45958.333333333299</v>
+      </c>
+      <c r="H37" s="4">
+        <v>45960.708333333299</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J37" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K37" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38" spans="1:11">
       <c r="A38" t="s">
+        <v>90</v>
+      </c>
+      <c r="B38" t="s">
         <v>91</v>
       </c>
-      <c r="B38" t="s">
-        <v>92</v>
-      </c>
       <c r="C38" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D38" s="3">
-        <v>45958.333333333299</v>
-      </c>
-      <c r="E38" s="3">
-        <v>45960.708333333299</v>
+        <v>5</v>
+      </c>
+      <c r="D38" s="4">
+        <v>46010.333333333299</v>
+      </c>
+      <c r="E38" s="4">
+        <v>46010.333333333299</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G38" s="3">
-        <v>45958.333333333299</v>
-      </c>
-      <c r="H38" s="3">
-        <v>45960.708333333299</v>
+        <v>14</v>
+      </c>
+      <c r="G38" s="4">
+        <v>46010.333333333299</v>
+      </c>
+      <c r="H38" s="4">
+        <v>46010.333333333299</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J38" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K38" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39" spans="1:11">
       <c r="A39" t="s">
+        <v>92</v>
+      </c>
+      <c r="B39" t="s">
         <v>93</v>
       </c>
-      <c r="B39" t="s">
-        <v>94</v>
-      </c>
       <c r="C39" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D39" s="3">
-        <v>46010.333333333299</v>
-      </c>
-      <c r="E39" s="3">
-        <v>46010.333333333299</v>
+        <v>5</v>
+      </c>
+      <c r="D39" s="4">
+        <v>46000.333333333299</v>
+      </c>
+      <c r="E39" s="4">
+        <v>46002.708333333299</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G39" s="3">
-        <v>46010.333333333299</v>
-      </c>
-      <c r="H39" s="3">
-        <v>46010.333333333299</v>
+        <v>14</v>
+      </c>
+      <c r="G39" s="4">
+        <v>46000.333333333299</v>
+      </c>
+      <c r="H39" s="4">
+        <v>46002.708333333299</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J39" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K39" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40" spans="1:11">
       <c r="A40" t="s">
+        <v>94</v>
+      </c>
+      <c r="B40" t="s">
         <v>95</v>
       </c>
-      <c r="B40" t="s">
-        <v>96</v>
-      </c>
       <c r="C40" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D40" s="3">
-        <v>46000.333333333299</v>
-      </c>
-      <c r="E40" s="3">
-        <v>46002.708333333299</v>
+        <v>5</v>
+      </c>
+      <c r="D40" s="4">
+        <v>45992.333333333299</v>
+      </c>
+      <c r="E40" s="4">
+        <v>45996.708333333299</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G40" s="3">
-        <v>46000.333333333299</v>
-      </c>
-      <c r="H40" s="3">
-        <v>46002.708333333299</v>
+        <v>14</v>
+      </c>
+      <c r="G40" s="4">
+        <v>45992.333333333299</v>
+      </c>
+      <c r="H40" s="4">
+        <v>45996.708333333299</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J40" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K40" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41" spans="1:11">
       <c r="A41" t="s">
+        <v>96</v>
+      </c>
+      <c r="B41" t="s">
         <v>97</v>
       </c>
-      <c r="B41" t="s">
-        <v>98</v>
-      </c>
       <c r="C41" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D41" s="3">
-        <v>45992.333333333299</v>
-      </c>
-      <c r="E41" s="3">
-        <v>45996.708333333299</v>
+        <v>5</v>
+      </c>
+      <c r="D41" s="4">
+        <v>45974.333333333299</v>
+      </c>
+      <c r="E41" s="4">
+        <v>45989.708333333299</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G41" s="3">
-        <v>45992.333333333299</v>
-      </c>
-      <c r="H41" s="3">
-        <v>45996.708333333299</v>
+        <v>14</v>
+      </c>
+      <c r="G41" s="4">
+        <v>45974.333333333299</v>
+      </c>
+      <c r="H41" s="4">
+        <v>45989.708333333299</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J41" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K41" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42" spans="1:11">
       <c r="A42" t="s">
+        <v>98</v>
+      </c>
+      <c r="B42" t="s">
         <v>99</v>
       </c>
-      <c r="B42" t="s">
-        <v>100</v>
-      </c>
       <c r="C42" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D42" s="3">
-        <v>45974.333333333299</v>
-      </c>
-      <c r="E42" s="3">
+        <v>5</v>
+      </c>
+      <c r="D42" s="4">
+        <v>45980.333333333299</v>
+      </c>
+      <c r="E42" s="4">
         <v>45989.708333333299</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G42" s="3">
-        <v>45974.333333333299</v>
-      </c>
-      <c r="H42" s="3">
+        <v>14</v>
+      </c>
+      <c r="G42" s="4">
+        <v>45980.333333333299</v>
+      </c>
+      <c r="H42" s="4">
         <v>45989.708333333299</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J42" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K42" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="43" spans="1:11">
       <c r="A43" t="s">
+        <v>100</v>
+      </c>
+      <c r="B43" t="s">
         <v>101</v>
       </c>
-      <c r="B43" t="s">
-        <v>102</v>
-      </c>
       <c r="C43" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D43" s="3">
-        <v>45980.333333333299</v>
-      </c>
-      <c r="E43" s="3">
-        <v>45989.708333333299</v>
+        <v>5</v>
+      </c>
+      <c r="D43" s="4">
+        <v>45972.333333333299</v>
+      </c>
+      <c r="E43" s="4">
+        <v>45975.333333333299</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G43" s="3">
-        <v>45980.333333333299</v>
-      </c>
-      <c r="H43" s="3">
-        <v>45989.708333333299</v>
+        <v>14</v>
+      </c>
+      <c r="G43" s="4">
+        <v>45972.333333333299</v>
+      </c>
+      <c r="H43" s="4">
+        <v>45975.333333333299</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J43" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K43" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44" spans="1:11">
       <c r="A44" t="s">
+        <v>102</v>
+      </c>
+      <c r="B44" t="s">
         <v>103</v>
       </c>
-      <c r="B44" t="s">
-        <v>104</v>
-      </c>
       <c r="C44" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D44" s="3">
-        <v>45972.333333333299</v>
-      </c>
-      <c r="E44" s="3">
-        <v>45975.333333333299</v>
+        <v>5</v>
+      </c>
+      <c r="D44" s="4">
+        <v>45992.333333333299</v>
+      </c>
+      <c r="E44" s="4">
+        <v>46010.708333333299</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G44" s="3">
-        <v>45972.333333333299</v>
-      </c>
-      <c r="H44" s="3">
-        <v>45975.333333333299</v>
+        <v>14</v>
+      </c>
+      <c r="G44" s="4">
+        <v>45992.333333333299</v>
+      </c>
+      <c r="H44" s="4">
+        <v>46010.708333333299</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J44" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K44" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45" spans="1:11">
       <c r="A45" t="s">
+        <v>104</v>
+      </c>
+      <c r="B45" t="s">
         <v>105</v>
       </c>
-      <c r="B45" t="s">
-        <v>106</v>
-      </c>
       <c r="C45" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D45" s="3">
-        <v>45992.333333333299</v>
-      </c>
-      <c r="E45" s="3">
-        <v>46010.708333333299</v>
+        <v>5</v>
+      </c>
+      <c r="D45" s="4">
+        <v>45964.333333333299</v>
+      </c>
+      <c r="E45" s="4">
+        <v>45966.708333333299</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G45" s="3">
-        <v>45992.333333333299</v>
-      </c>
-      <c r="H45" s="3">
-        <v>46010.708333333299</v>
+        <v>14</v>
+      </c>
+      <c r="G45" s="4">
+        <v>45964.333333333299</v>
+      </c>
+      <c r="H45" s="4">
+        <v>45966.708333333299</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J45" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K45" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46" spans="1:11">
       <c r="A46" t="s">
+        <v>106</v>
+      </c>
+      <c r="B46" t="s">
         <v>107</v>
       </c>
-      <c r="B46" t="s">
-        <v>108</v>
-      </c>
       <c r="C46" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D46" s="3">
-        <v>45964.333333333299</v>
-      </c>
-      <c r="E46" s="3">
-        <v>45966.708333333299</v>
+        <v>5</v>
+      </c>
+      <c r="D46" s="4">
+        <v>45978.333333333299</v>
+      </c>
+      <c r="E46" s="4">
+        <v>45988.708333333299</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G46" s="3">
-        <v>45964.333333333299</v>
-      </c>
-      <c r="H46" s="3">
-        <v>45966.708333333299</v>
+        <v>14</v>
+      </c>
+      <c r="G46" s="4">
+        <v>45978.333333333299</v>
+      </c>
+      <c r="H46" s="4">
+        <v>45988.708333333299</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J46" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K46" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47" spans="1:11">
       <c r="A47" t="s">
+        <v>108</v>
+      </c>
+      <c r="B47" t="s">
         <v>109</v>
       </c>
-      <c r="B47" t="s">
-        <v>110</v>
-      </c>
       <c r="C47" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D47" s="3">
-        <v>45978.333333333299</v>
-      </c>
-      <c r="E47" s="3">
-        <v>45988.708333333299</v>
+        <v>5</v>
+      </c>
+      <c r="D47" s="4">
+        <v>45937.333333333299</v>
+      </c>
+      <c r="E47" s="4">
+        <v>45943.708333333299</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G47" s="3">
-        <v>45978.333333333299</v>
-      </c>
-      <c r="H47" s="3">
-        <v>45988.708333333299</v>
+        <v>14</v>
+      </c>
+      <c r="G47" s="4">
+        <v>45937.333333333299</v>
+      </c>
+      <c r="H47" s="4">
+        <v>45943.708333333299</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J47" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K47" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="48" spans="1:11">
       <c r="A48" t="s">
+        <v>110</v>
+      </c>
+      <c r="B48" t="s">
         <v>111</v>
       </c>
-      <c r="B48" t="s">
-        <v>112</v>
-      </c>
       <c r="C48" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D48" s="3">
-        <v>45937.333333333299</v>
-      </c>
-      <c r="E48" s="3">
-        <v>45943.708333333299</v>
+        <v>5</v>
+      </c>
+      <c r="D48" s="4">
+        <v>45957.333333333299</v>
+      </c>
+      <c r="E48" s="4">
+        <v>45957.708333333299</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G48" s="3">
-        <v>45937.333333333299</v>
-      </c>
-      <c r="H48" s="3">
-        <v>45943.708333333299</v>
+        <v>14</v>
+      </c>
+      <c r="G48" s="4">
+        <v>45957.333333333299</v>
+      </c>
+      <c r="H48" s="4">
+        <v>45957.708333333299</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J48" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K48" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="49" spans="1:11">
       <c r="A49" t="s">
+        <v>112</v>
+      </c>
+      <c r="B49" t="s">
         <v>113</v>
       </c>
-      <c r="B49" t="s">
-        <v>114</v>
-      </c>
       <c r="C49" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D49" s="3">
-        <v>45957.333333333299</v>
-      </c>
-      <c r="E49" s="3">
-        <v>45957.708333333299</v>
+        <v>5</v>
+      </c>
+      <c r="D49" s="4">
+        <v>45947.333333333299</v>
+      </c>
+      <c r="E49" s="4">
+        <v>45947.333333333299</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G49" s="3">
-        <v>45957.333333333299</v>
-      </c>
-      <c r="H49" s="3">
-        <v>45957.708333333299</v>
+        <v>14</v>
+      </c>
+      <c r="G49" s="4">
+        <v>45947.333333333299</v>
+      </c>
+      <c r="H49" s="4">
+        <v>45947.333333333299</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J49" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K49" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50" spans="1:11">
       <c r="A50" t="s">
+        <v>114</v>
+      </c>
+      <c r="B50" t="s">
         <v>115</v>
       </c>
-      <c r="B50" t="s">
-        <v>116</v>
-      </c>
       <c r="C50" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D50" s="3">
-        <v>45947.333333333299</v>
-      </c>
-      <c r="E50" s="3">
-        <v>45947.333333333299</v>
+        <v>5</v>
+      </c>
+      <c r="D50" s="4">
+        <v>45919.333333333299</v>
+      </c>
+      <c r="E50" s="4">
+        <v>45946.708333333299</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G50" s="3">
-        <v>45947.333333333299</v>
-      </c>
-      <c r="H50" s="3">
-        <v>45947.333333333299</v>
+        <v>14</v>
+      </c>
+      <c r="G50" s="4">
+        <v>45919.333333333299</v>
+      </c>
+      <c r="H50" s="4">
+        <v>45946.708333333299</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J50" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K50" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="51" spans="1:11">
       <c r="A51" t="s">
+        <v>116</v>
+      </c>
+      <c r="B51" t="s">
         <v>117</v>
       </c>
-      <c r="B51" t="s">
-        <v>118</v>
-      </c>
       <c r="C51" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D51" s="3">
-        <v>45919.333333333299</v>
-      </c>
-      <c r="E51" s="3">
-        <v>45946.708333333299</v>
+        <v>5</v>
+      </c>
+      <c r="D51" s="4">
+        <v>46083.333333333299</v>
+      </c>
+      <c r="E51" s="4">
+        <v>46090.708333333299</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G51" s="3">
-        <v>45919.333333333299</v>
-      </c>
-      <c r="H51" s="3">
-        <v>45946.708333333299</v>
+        <v>14</v>
+      </c>
+      <c r="G51" s="4">
+        <v>46083.333333333299</v>
+      </c>
+      <c r="H51" s="4">
+        <v>46090.708333333299</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J51" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K51" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="52" spans="1:11">
       <c r="A52" t="s">
+        <v>118</v>
+      </c>
+      <c r="B52" t="s">
         <v>119</v>
       </c>
-      <c r="B52" t="s">
+      <c r="C52" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="C52" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D52" s="3">
-        <v>46083.333333333299</v>
-      </c>
-      <c r="E52" s="3">
-        <v>46090.708333333299</v>
+      <c r="D52" s="4">
+        <v>46184.333333333299</v>
+      </c>
+      <c r="E52" s="4">
+        <v>46191.708333333299</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G52" s="3">
-        <v>46083.333333333299</v>
-      </c>
-      <c r="H52" s="3">
-        <v>46090.708333333299</v>
+        <v>5</v>
+      </c>
+      <c r="G52" s="4">
+        <v>46162.333333333299</v>
+      </c>
+      <c r="H52" s="4">
+        <v>46170.708333333299</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>6</v>
+        <v>75</v>
       </c>
       <c r="J52" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K52" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="53" spans="1:11">
@@ -2913,29 +2913,29 @@
       <c r="C53" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="D53" s="3">
-        <v>46184.333333333299</v>
-      </c>
-      <c r="E53" s="3">
-        <v>46191.708333333299</v>
+      <c r="D53" s="4">
+        <v>46181.333333333299</v>
+      </c>
+      <c r="E53" s="4">
+        <v>46183.708333333299</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G53" s="3">
-        <v>46162.333333333299</v>
-      </c>
-      <c r="H53" s="3">
-        <v>46170.708333333299</v>
+        <v>5</v>
+      </c>
+      <c r="G53" s="4">
+        <v>46157.333333333299</v>
+      </c>
+      <c r="H53" s="4">
+        <v>46161.708333333299</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="J53" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K53" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="54" spans="1:11">
@@ -2946,1536 +2946,1501 @@
         <v>125</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="D54" s="3">
-        <v>46181.333333333299</v>
-      </c>
-      <c r="E54" s="3">
-        <v>46183.708333333299</v>
+        <v>30</v>
+      </c>
+      <c r="D54" s="4">
+        <v>46177.333333333299</v>
+      </c>
+      <c r="E54" s="4">
+        <v>46178.708333333299</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G54" s="3">
-        <v>46157.333333333299</v>
-      </c>
-      <c r="H54" s="3">
-        <v>46161.708333333299</v>
+        <v>5</v>
+      </c>
+      <c r="G54" s="4">
+        <v>46155.333333333299</v>
+      </c>
+      <c r="H54" s="4">
+        <v>46156.708333333299</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="J54" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K54" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="55" spans="1:11">
       <c r="A55" t="s">
+        <v>126</v>
+      </c>
+      <c r="B55" t="s">
         <v>127</v>
       </c>
-      <c r="B55" t="s">
-        <v>128</v>
-      </c>
       <c r="C55" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D55" s="3">
-        <v>46177.333333333299</v>
-      </c>
-      <c r="E55" s="3">
-        <v>46178.708333333299</v>
+        <v>30</v>
+      </c>
+      <c r="D55" s="4">
+        <v>46175.333333333299</v>
+      </c>
+      <c r="E55" s="4">
+        <v>46176.708333333299</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G55" s="3">
-        <v>46155.333333333299</v>
-      </c>
-      <c r="H55" s="3">
-        <v>46156.708333333299</v>
+        <v>5</v>
+      </c>
+      <c r="G55" s="4">
+        <v>46153.333333333299</v>
+      </c>
+      <c r="H55" s="4">
+        <v>46154.708333333299</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="J55" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K55" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="56" spans="1:11">
       <c r="A56" t="s">
+        <v>128</v>
+      </c>
+      <c r="B56" t="s">
         <v>129</v>
       </c>
-      <c r="B56" t="s">
-        <v>130</v>
-      </c>
       <c r="C56" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D56" s="3">
-        <v>46175.333333333299</v>
-      </c>
-      <c r="E56" s="3">
-        <v>46176.708333333299</v>
+        <v>30</v>
+      </c>
+      <c r="D56" s="4">
+        <v>46171.333333333299</v>
+      </c>
+      <c r="E56" s="4">
+        <v>46174.708333333299</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G56" s="3">
-        <v>46153.333333333299</v>
-      </c>
-      <c r="H56" s="3">
-        <v>46154.708333333299</v>
+        <v>5</v>
+      </c>
+      <c r="G56" s="4">
+        <v>46149.333333333299</v>
+      </c>
+      <c r="H56" s="4">
+        <v>46150.708333333299</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="J56" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K56" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="57" spans="1:11">
       <c r="A57" t="s">
+        <v>130</v>
+      </c>
+      <c r="B57" t="s">
         <v>131</v>
       </c>
-      <c r="B57" t="s">
-        <v>132</v>
-      </c>
       <c r="C57" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D57" s="3">
-        <v>46171.333333333299</v>
-      </c>
-      <c r="E57" s="3">
-        <v>46174.708333333299</v>
+        <v>30</v>
+      </c>
+      <c r="D57" s="4">
+        <v>46169.333333333299</v>
+      </c>
+      <c r="E57" s="4">
+        <v>46170.708333333299</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G57" s="3">
-        <v>46149.333333333299</v>
-      </c>
-      <c r="H57" s="3">
-        <v>46150.708333333299</v>
+        <v>5</v>
+      </c>
+      <c r="G57" s="4">
+        <v>46147.333333333299</v>
+      </c>
+      <c r="H57" s="4">
+        <v>46148.708333333299</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="J57" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K57" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="58" spans="1:11">
       <c r="A58" t="s">
+        <v>132</v>
+      </c>
+      <c r="B58" t="s">
         <v>133</v>
       </c>
-      <c r="B58" t="s">
-        <v>134</v>
-      </c>
       <c r="C58" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D58" s="3">
-        <v>46169.333333333299</v>
-      </c>
-      <c r="E58" s="3">
-        <v>46170.708333333299</v>
+        <v>43</v>
+      </c>
+      <c r="D58" s="4">
+        <v>46168.333333333299</v>
+      </c>
+      <c r="E58" s="4">
+        <v>46168.708333333299</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G58" s="3">
-        <v>46147.333333333299</v>
-      </c>
-      <c r="H58" s="3">
-        <v>46148.708333333299</v>
+        <v>5</v>
+      </c>
+      <c r="G58" s="4">
+        <v>46143.333333333299</v>
+      </c>
+      <c r="H58" s="4">
+        <v>46143.708333333299</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="J58" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K58" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="59" spans="1:11">
       <c r="A59" t="s">
+        <v>134</v>
+      </c>
+      <c r="B59" t="s">
         <v>135</v>
       </c>
-      <c r="B59" t="s">
+      <c r="C59" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="C59" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D59" s="3">
-        <v>46168.333333333299</v>
-      </c>
-      <c r="E59" s="3">
-        <v>46168.708333333299</v>
+      <c r="D59" s="4">
+        <v>46112.333333333299</v>
+      </c>
+      <c r="E59" s="4">
+        <v>46167.708333333299</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G59" s="3">
-        <v>46143.333333333299</v>
-      </c>
-      <c r="H59" s="3">
-        <v>46143.708333333299</v>
+        <v>5</v>
+      </c>
+      <c r="G59" s="4">
+        <v>46112.333333333299</v>
+      </c>
+      <c r="H59" s="4">
+        <v>46142.708333333299</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>78</v>
+        <v>137</v>
       </c>
       <c r="J59" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K59" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="60" spans="1:11">
       <c r="A60" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B60" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="D60" s="3">
-        <v>46112.333333333299</v>
-      </c>
-      <c r="E60" s="3">
-        <v>46167.708333333299</v>
+        <v>5</v>
+      </c>
+      <c r="D60" s="4">
+        <v>46111.333333333299</v>
+      </c>
+      <c r="E60" s="4">
+        <v>46111.708333333299</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G60" s="3">
-        <v>46112.333333333299</v>
-      </c>
-      <c r="H60" s="3">
-        <v>46142.708333333299</v>
+        <v>14</v>
+      </c>
+      <c r="G60" s="4">
+        <v>46111.333333333299</v>
+      </c>
+      <c r="H60" s="4">
+        <v>46111.708333333299</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>140</v>
+        <v>5</v>
       </c>
       <c r="J60" t="s">
         <v>6</v>
       </c>
       <c r="K60" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="61" spans="1:11">
       <c r="A61" t="s">
+        <v>140</v>
+      </c>
+      <c r="B61" t="s">
         <v>141</v>
       </c>
-      <c r="B61" t="s">
-        <v>142</v>
-      </c>
       <c r="C61" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D61" s="3">
-        <v>46111.333333333299</v>
-      </c>
-      <c r="E61" s="3">
-        <v>46111.708333333299</v>
+        <v>5</v>
+      </c>
+      <c r="D61" s="4">
+        <v>46080.333333333299</v>
+      </c>
+      <c r="E61" s="4">
+        <v>46080.708333333299</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G61" s="3">
-        <v>46111.333333333299</v>
-      </c>
-      <c r="H61" s="3">
-        <v>46111.708333333299</v>
+        <v>14</v>
+      </c>
+      <c r="G61" s="4">
+        <v>46080.333333333299</v>
+      </c>
+      <c r="H61" s="4">
+        <v>46080.708333333299</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J61" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K61" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="62" spans="1:11">
       <c r="A62" t="s">
+        <v>142</v>
+      </c>
+      <c r="B62" t="s">
         <v>143</v>
       </c>
-      <c r="B62" t="s">
-        <v>144</v>
-      </c>
       <c r="C62" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D62" s="3">
+        <v>5</v>
+      </c>
+      <c r="D62" s="4">
         <v>46080.333333333299</v>
       </c>
-      <c r="E62" s="3">
+      <c r="E62" s="4">
         <v>46080.708333333299</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G62" s="3">
+        <v>14</v>
+      </c>
+      <c r="G62" s="4">
         <v>46080.333333333299</v>
       </c>
-      <c r="H62" s="3">
+      <c r="H62" s="4">
         <v>46080.708333333299</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J62" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K62" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="63" spans="1:11">
       <c r="A63" t="s">
+        <v>144</v>
+      </c>
+      <c r="B63" t="s">
         <v>145</v>
       </c>
-      <c r="B63" t="s">
-        <v>146</v>
-      </c>
       <c r="C63" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D63" s="3">
+        <v>5</v>
+      </c>
+      <c r="D63" s="4">
         <v>46080.333333333299</v>
       </c>
-      <c r="E63" s="3">
+      <c r="E63" s="4">
         <v>46080.708333333299</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G63" s="3">
+        <v>14</v>
+      </c>
+      <c r="G63" s="4">
         <v>46080.333333333299</v>
       </c>
-      <c r="H63" s="3">
+      <c r="H63" s="4">
         <v>46080.708333333299</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J63" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K63" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="64" spans="1:11">
       <c r="A64" t="s">
+        <v>146</v>
+      </c>
+      <c r="B64" t="s">
         <v>147</v>
       </c>
-      <c r="B64" t="s">
-        <v>148</v>
-      </c>
       <c r="C64" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D64" s="3">
-        <v>46080.333333333299</v>
-      </c>
-      <c r="E64" s="3">
+        <v>5</v>
+      </c>
+      <c r="D64" s="4">
+        <v>46076.333333333299</v>
+      </c>
+      <c r="E64" s="4">
         <v>46080.708333333299</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G64" s="3">
-        <v>46080.333333333299</v>
-      </c>
-      <c r="H64" s="3">
+        <v>14</v>
+      </c>
+      <c r="G64" s="4">
+        <v>46076.333333333299</v>
+      </c>
+      <c r="H64" s="4">
         <v>46080.708333333299</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J64" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K64" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="65" spans="1:11">
       <c r="A65" t="s">
+        <v>148</v>
+      </c>
+      <c r="B65" t="s">
         <v>149</v>
       </c>
-      <c r="B65" t="s">
-        <v>150</v>
-      </c>
       <c r="C65" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D65" s="3">
-        <v>46076.333333333299</v>
-      </c>
-      <c r="E65" s="3">
-        <v>46080.708333333299</v>
+        <v>5</v>
+      </c>
+      <c r="D65" s="4">
+        <v>46073.333333333299</v>
+      </c>
+      <c r="E65" s="4">
+        <v>46073.708333333299</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G65" s="3">
-        <v>46076.333333333299</v>
-      </c>
-      <c r="H65" s="3">
-        <v>46080.708333333299</v>
+        <v>14</v>
+      </c>
+      <c r="G65" s="4">
+        <v>46073.333333333299</v>
+      </c>
+      <c r="H65" s="4">
+        <v>46073.708333333299</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J65" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K65" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="66" spans="1:11">
       <c r="A66" t="s">
+        <v>150</v>
+      </c>
+      <c r="B66" t="s">
         <v>151</v>
       </c>
-      <c r="B66" t="s">
-        <v>152</v>
-      </c>
       <c r="C66" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D66" s="3">
-        <v>46073.333333333299</v>
-      </c>
-      <c r="E66" s="3">
+        <v>5</v>
+      </c>
+      <c r="D66" s="4">
+        <v>46071.333333333299</v>
+      </c>
+      <c r="E66" s="4">
         <v>46073.708333333299</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G66" s="3">
-        <v>46073.333333333299</v>
-      </c>
-      <c r="H66" s="3">
+        <v>14</v>
+      </c>
+      <c r="G66" s="4">
+        <v>46071.333333333299</v>
+      </c>
+      <c r="H66" s="4">
         <v>46073.708333333299</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J66" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K66" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="67" spans="1:11">
       <c r="A67" t="s">
+        <v>152</v>
+      </c>
+      <c r="B67" t="s">
         <v>153</v>
       </c>
-      <c r="B67" t="s">
-        <v>154</v>
-      </c>
       <c r="C67" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D67" s="3">
+        <v>5</v>
+      </c>
+      <c r="D67" s="4">
         <v>46071.333333333299</v>
       </c>
-      <c r="E67" s="3">
-        <v>46073.708333333299</v>
+      <c r="E67" s="4">
+        <v>46071.333333333299</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G67" s="3">
+        <v>14</v>
+      </c>
+      <c r="G67" s="4">
         <v>46071.333333333299</v>
       </c>
-      <c r="H67" s="3">
-        <v>46073.708333333299</v>
+      <c r="H67" s="4">
+        <v>46071.333333333299</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J67" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K67" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="68" spans="1:11">
       <c r="A68" t="s">
+        <v>154</v>
+      </c>
+      <c r="B68" t="s">
         <v>155</v>
       </c>
-      <c r="B68" t="s">
-        <v>156</v>
-      </c>
       <c r="C68" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D68" s="3">
-        <v>46071.333333333299</v>
-      </c>
-      <c r="E68" s="3">
-        <v>46071.333333333299</v>
+        <v>5</v>
+      </c>
+      <c r="D68" s="4">
+        <v>46069.333333333299</v>
+      </c>
+      <c r="E68" s="4">
+        <v>46070.708333333299</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G68" s="3">
-        <v>46071.333333333299</v>
-      </c>
-      <c r="H68" s="3">
-        <v>46071.333333333299</v>
+        <v>14</v>
+      </c>
+      <c r="G68" s="4">
+        <v>46069.333333333299</v>
+      </c>
+      <c r="H68" s="4">
+        <v>46070.708333333299</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J68" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K68" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="69" spans="1:11">
       <c r="A69" t="s">
+        <v>156</v>
+      </c>
+      <c r="B69" t="s">
         <v>157</v>
       </c>
-      <c r="B69" t="s">
-        <v>158</v>
-      </c>
       <c r="C69" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D69" s="3">
-        <v>46069.333333333299</v>
-      </c>
-      <c r="E69" s="3">
-        <v>46070.708333333299</v>
+        <v>5</v>
+      </c>
+      <c r="D69" s="4">
+        <v>46066.333333333299</v>
+      </c>
+      <c r="E69" s="4">
+        <v>46071.708333333299</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G69" s="3">
-        <v>46069.333333333299</v>
-      </c>
-      <c r="H69" s="3">
-        <v>46070.708333333299</v>
+        <v>14</v>
+      </c>
+      <c r="G69" s="4">
+        <v>46066.333333333299</v>
+      </c>
+      <c r="H69" s="4">
+        <v>46071.708333333299</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J69" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K69" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="70" spans="1:11">
       <c r="A70" t="s">
+        <v>158</v>
+      </c>
+      <c r="B70" t="s">
         <v>159</v>
       </c>
-      <c r="B70" t="s">
-        <v>160</v>
-      </c>
       <c r="C70" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D70" s="3">
-        <v>46066.333333333299</v>
-      </c>
-      <c r="E70" s="3">
-        <v>46071.708333333299</v>
+        <v>5</v>
+      </c>
+      <c r="D70" s="4">
+        <v>46062.333333333299</v>
+      </c>
+      <c r="E70" s="4">
+        <v>46065.708333333299</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G70" s="3">
-        <v>46066.333333333299</v>
-      </c>
-      <c r="H70" s="3">
-        <v>46071.708333333299</v>
+        <v>14</v>
+      </c>
+      <c r="G70" s="4">
+        <v>46062.333333333299</v>
+      </c>
+      <c r="H70" s="4">
+        <v>46065.708333333299</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J70" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K70" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="71" spans="1:11">
       <c r="A71" t="s">
+        <v>160</v>
+      </c>
+      <c r="B71" t="s">
         <v>161</v>
       </c>
-      <c r="B71" t="s">
-        <v>162</v>
-      </c>
       <c r="C71" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D71" s="3">
-        <v>46062.333333333299</v>
-      </c>
-      <c r="E71" s="3">
-        <v>46065.708333333299</v>
+        <v>5</v>
+      </c>
+      <c r="D71" s="4">
+        <v>46057.333333333299</v>
+      </c>
+      <c r="E71" s="4">
+        <v>46062.708333333299</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G71" s="3">
-        <v>46062.333333333299</v>
-      </c>
-      <c r="H71" s="3">
-        <v>46065.708333333299</v>
+        <v>14</v>
+      </c>
+      <c r="G71" s="4">
+        <v>46057.333333333299</v>
+      </c>
+      <c r="H71" s="4">
+        <v>46062.708333333299</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J71" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K71" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="72" spans="1:11">
       <c r="A72" t="s">
+        <v>162</v>
+      </c>
+      <c r="B72" t="s">
         <v>163</v>
       </c>
-      <c r="B72" t="s">
-        <v>164</v>
-      </c>
       <c r="C72" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D72" s="3">
-        <v>46057.333333333299</v>
-      </c>
-      <c r="E72" s="3">
-        <v>46062.708333333299</v>
+        <v>5</v>
+      </c>
+      <c r="D72" s="4">
+        <v>46055.333333333299</v>
+      </c>
+      <c r="E72" s="4">
+        <v>46055.708333333299</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G72" s="3">
-        <v>46057.333333333299</v>
-      </c>
-      <c r="H72" s="3">
-        <v>46062.708333333299</v>
+        <v>14</v>
+      </c>
+      <c r="G72" s="4">
+        <v>46055.333333333299</v>
+      </c>
+      <c r="H72" s="4">
+        <v>46055.708333333299</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J72" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K72" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="73" spans="1:11">
       <c r="A73" t="s">
+        <v>164</v>
+      </c>
+      <c r="B73" t="s">
         <v>165</v>
       </c>
-      <c r="B73" t="s">
-        <v>166</v>
-      </c>
       <c r="C73" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D73" s="3">
-        <v>46055.333333333299</v>
-      </c>
-      <c r="E73" s="3">
-        <v>46055.708333333299</v>
+        <v>5</v>
+      </c>
+      <c r="D73" s="4">
+        <v>46052.333333333299</v>
+      </c>
+      <c r="E73" s="4">
+        <v>46052.333333333299</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G73" s="3">
-        <v>46055.333333333299</v>
-      </c>
-      <c r="H73" s="3">
-        <v>46055.708333333299</v>
+        <v>14</v>
+      </c>
+      <c r="G73" s="4">
+        <v>46052.333333333299</v>
+      </c>
+      <c r="H73" s="4">
+        <v>46052.333333333299</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J73" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K73" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="74" spans="1:11">
       <c r="A74" t="s">
+        <v>166</v>
+      </c>
+      <c r="B74" t="s">
         <v>167</v>
       </c>
-      <c r="B74" t="s">
-        <v>168</v>
-      </c>
       <c r="C74" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D74" s="3">
-        <v>46052.333333333299</v>
-      </c>
-      <c r="E74" s="3">
-        <v>46052.333333333299</v>
+        <v>5</v>
+      </c>
+      <c r="D74" s="4">
+        <v>46051.333333333299</v>
+      </c>
+      <c r="E74" s="4">
+        <v>46051.708333333299</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G74" s="3">
-        <v>46052.333333333299</v>
-      </c>
-      <c r="H74" s="3">
-        <v>46052.333333333299</v>
+        <v>14</v>
+      </c>
+      <c r="G74" s="4">
+        <v>46051.333333333299</v>
+      </c>
+      <c r="H74" s="4">
+        <v>46051.708333333299</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J74" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K74" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="75" spans="1:11">
       <c r="A75" t="s">
+        <v>168</v>
+      </c>
+      <c r="B75" t="s">
         <v>169</v>
       </c>
-      <c r="B75" t="s">
-        <v>170</v>
-      </c>
       <c r="C75" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D75" s="3">
-        <v>46051.333333333299</v>
-      </c>
-      <c r="E75" s="3">
-        <v>46051.708333333299</v>
+        <v>5</v>
+      </c>
+      <c r="D75" s="4">
+        <v>46050.333333333299</v>
+      </c>
+      <c r="E75" s="4">
+        <v>46050.708333333299</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G75" s="3">
-        <v>46051.333333333299</v>
-      </c>
-      <c r="H75" s="3">
-        <v>46051.708333333299</v>
+        <v>14</v>
+      </c>
+      <c r="G75" s="4">
+        <v>46050.333333333299</v>
+      </c>
+      <c r="H75" s="4">
+        <v>46050.708333333299</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J75" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K75" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="76" spans="1:11">
       <c r="A76" t="s">
+        <v>170</v>
+      </c>
+      <c r="B76" t="s">
         <v>171</v>
       </c>
-      <c r="B76" t="s">
-        <v>172</v>
-      </c>
       <c r="C76" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D76" s="3">
+        <v>5</v>
+      </c>
+      <c r="D76" s="4">
         <v>46050.333333333299</v>
       </c>
-      <c r="E76" s="3">
-        <v>46050.708333333299</v>
+      <c r="E76" s="4">
+        <v>46052.708333333299</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G76" s="3">
+        <v>14</v>
+      </c>
+      <c r="G76" s="4">
         <v>46050.333333333299</v>
       </c>
-      <c r="H76" s="3">
-        <v>46050.708333333299</v>
+      <c r="H76" s="4">
+        <v>46052.708333333299</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J76" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K76" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="77" spans="1:11">
       <c r="A77" t="s">
+        <v>172</v>
+      </c>
+      <c r="B77" t="s">
         <v>173</v>
       </c>
-      <c r="B77" t="s">
-        <v>174</v>
-      </c>
       <c r="C77" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D77" s="3">
-        <v>46050.333333333299</v>
-      </c>
-      <c r="E77" s="3">
-        <v>46052.708333333299</v>
+        <v>5</v>
+      </c>
+      <c r="D77" s="4">
+        <v>46048.333333333299</v>
+      </c>
+      <c r="E77" s="4">
+        <v>46049.708333333299</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G77" s="3">
-        <v>46050.333333333299</v>
-      </c>
-      <c r="H77" s="3">
-        <v>46052.708333333299</v>
+        <v>14</v>
+      </c>
+      <c r="G77" s="4">
+        <v>46048.333333333299</v>
+      </c>
+      <c r="H77" s="4">
+        <v>46049.708333333299</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J77" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K77" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="78" spans="1:11">
       <c r="A78" t="s">
+        <v>174</v>
+      </c>
+      <c r="B78" t="s">
         <v>175</v>
       </c>
-      <c r="B78" t="s">
-        <v>176</v>
-      </c>
       <c r="C78" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D78" s="3">
+        <v>5</v>
+      </c>
+      <c r="D78" s="4">
         <v>46048.333333333299</v>
       </c>
-      <c r="E78" s="3">
-        <v>46049.708333333299</v>
+      <c r="E78" s="4">
+        <v>46052.708333333299</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G78" s="3">
+        <v>14</v>
+      </c>
+      <c r="G78" s="4">
         <v>46048.333333333299</v>
       </c>
-      <c r="H78" s="3">
-        <v>46049.708333333299</v>
+      <c r="H78" s="4">
+        <v>46052.708333333299</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J78" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K78" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="79" spans="1:11">
       <c r="A79" t="s">
+        <v>176</v>
+      </c>
+      <c r="B79" t="s">
         <v>177</v>
       </c>
-      <c r="B79" t="s">
-        <v>178</v>
-      </c>
       <c r="C79" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D79" s="3">
+        <v>5</v>
+      </c>
+      <c r="D79" s="4">
         <v>46048.333333333299</v>
       </c>
-      <c r="E79" s="3">
-        <v>46052.708333333299</v>
+      <c r="E79" s="4">
+        <v>46048.708333333299</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G79" s="3">
+        <v>14</v>
+      </c>
+      <c r="G79" s="4">
         <v>46048.333333333299</v>
       </c>
-      <c r="H79" s="3">
-        <v>46052.708333333299</v>
+      <c r="H79" s="4">
+        <v>46048.708333333299</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J79" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K79" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="80" spans="1:11">
       <c r="A80" t="s">
+        <v>178</v>
+      </c>
+      <c r="B80" t="s">
         <v>179</v>
       </c>
-      <c r="B80" t="s">
-        <v>180</v>
-      </c>
       <c r="C80" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D80" s="3">
-        <v>46048.333333333299</v>
-      </c>
-      <c r="E80" s="3">
-        <v>46048.708333333299</v>
+        <v>5</v>
+      </c>
+      <c r="D80" s="4">
+        <v>46045.333333333299</v>
+      </c>
+      <c r="E80" s="4">
+        <v>46045.708333333299</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G80" s="3">
-        <v>46048.333333333299</v>
-      </c>
-      <c r="H80" s="3">
-        <v>46048.708333333299</v>
+        <v>14</v>
+      </c>
+      <c r="G80" s="4">
+        <v>46045.333333333299</v>
+      </c>
+      <c r="H80" s="4">
+        <v>46045.708333333299</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J80" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K80" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="81" spans="1:11">
       <c r="A81" t="s">
+        <v>180</v>
+      </c>
+      <c r="B81" t="s">
         <v>181</v>
       </c>
-      <c r="B81" t="s">
-        <v>182</v>
-      </c>
       <c r="C81" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D81" s="3">
-        <v>46045.333333333299</v>
-      </c>
-      <c r="E81" s="3">
-        <v>46045.708333333299</v>
+        <v>5</v>
+      </c>
+      <c r="D81" s="4">
+        <v>46044.333333333299</v>
+      </c>
+      <c r="E81" s="4">
+        <v>46044.708333333299</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G81" s="3">
-        <v>46045.333333333299</v>
-      </c>
-      <c r="H81" s="3">
-        <v>46045.708333333299</v>
+        <v>14</v>
+      </c>
+      <c r="G81" s="4">
+        <v>46044.333333333299</v>
+      </c>
+      <c r="H81" s="4">
+        <v>46044.708333333299</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J81" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K81" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="82" spans="1:11">
       <c r="A82" t="s">
+        <v>182</v>
+      </c>
+      <c r="B82" t="s">
         <v>183</v>
       </c>
-      <c r="B82" t="s">
-        <v>184</v>
-      </c>
       <c r="C82" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D82" s="3">
-        <v>46044.333333333299</v>
-      </c>
-      <c r="E82" s="3">
-        <v>46044.708333333299</v>
+        <v>5</v>
+      </c>
+      <c r="D82" s="4">
+        <v>46043.333333333299</v>
+      </c>
+      <c r="E82" s="4">
+        <v>46043.708333333299</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G82" s="3">
-        <v>46044.333333333299</v>
-      </c>
-      <c r="H82" s="3">
-        <v>46044.708333333299</v>
+        <v>14</v>
+      </c>
+      <c r="G82" s="4">
+        <v>46043.333333333299</v>
+      </c>
+      <c r="H82" s="4">
+        <v>46043.708333333299</v>
       </c>
       <c r="I82" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J82" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K82" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="83" spans="1:11">
       <c r="A83" t="s">
+        <v>184</v>
+      </c>
+      <c r="B83" t="s">
         <v>185</v>
       </c>
-      <c r="B83" t="s">
-        <v>186</v>
-      </c>
       <c r="C83" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D83" s="3">
-        <v>46043.333333333299</v>
-      </c>
-      <c r="E83" s="3">
+        <v>5</v>
+      </c>
+      <c r="D83" s="4">
+        <v>46042.333333333299</v>
+      </c>
+      <c r="E83" s="4">
         <v>46043.708333333299</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G83" s="3">
-        <v>46043.333333333299</v>
-      </c>
-      <c r="H83" s="3">
+        <v>14</v>
+      </c>
+      <c r="G83" s="4">
+        <v>46042.333333333299</v>
+      </c>
+      <c r="H83" s="4">
         <v>46043.708333333299</v>
       </c>
       <c r="I83" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J83" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K83" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="84" spans="1:11">
       <c r="A84" t="s">
+        <v>186</v>
+      </c>
+      <c r="B84" t="s">
         <v>187</v>
       </c>
-      <c r="B84" t="s">
-        <v>188</v>
-      </c>
       <c r="C84" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D84" s="3">
+        <v>5</v>
+      </c>
+      <c r="D84" s="4">
         <v>46042.333333333299</v>
       </c>
-      <c r="E84" s="3">
+      <c r="E84" s="4">
         <v>46043.708333333299</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G84" s="3">
+        <v>14</v>
+      </c>
+      <c r="G84" s="4">
         <v>46042.333333333299</v>
       </c>
-      <c r="H84" s="3">
+      <c r="H84" s="4">
         <v>46043.708333333299</v>
       </c>
       <c r="I84" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J84" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K84" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="85" spans="1:11">
       <c r="A85" t="s">
+        <v>188</v>
+      </c>
+      <c r="B85" t="s">
         <v>189</v>
       </c>
-      <c r="B85" t="s">
-        <v>190</v>
-      </c>
       <c r="C85" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D85" s="3">
-        <v>46042.333333333299</v>
-      </c>
-      <c r="E85" s="3">
-        <v>46043.708333333299</v>
+        <v>5</v>
+      </c>
+      <c r="D85" s="4">
+        <v>46041.333333333299</v>
+      </c>
+      <c r="E85" s="4">
+        <v>46041.708333333299</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G85" s="3">
-        <v>46042.333333333299</v>
-      </c>
-      <c r="H85" s="3">
-        <v>46043.708333333299</v>
+        <v>14</v>
+      </c>
+      <c r="G85" s="4">
+        <v>46041.333333333299</v>
+      </c>
+      <c r="H85" s="4">
+        <v>46041.708333333299</v>
       </c>
       <c r="I85" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J85" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K85" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="86" spans="1:11">
       <c r="A86" t="s">
+        <v>190</v>
+      </c>
+      <c r="B86" t="s">
         <v>191</v>
       </c>
-      <c r="B86" t="s">
-        <v>192</v>
-      </c>
       <c r="C86" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D86" s="3">
+        <v>5</v>
+      </c>
+      <c r="D86" s="4">
         <v>46041.333333333299</v>
       </c>
-      <c r="E86" s="3">
+      <c r="E86" s="4">
         <v>46041.708333333299</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G86" s="3">
+        <v>14</v>
+      </c>
+      <c r="G86" s="4">
         <v>46041.333333333299</v>
       </c>
-      <c r="H86" s="3">
+      <c r="H86" s="4">
         <v>46041.708333333299</v>
       </c>
       <c r="I86" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J86" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K86" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="87" spans="1:11">
       <c r="A87" t="s">
+        <v>192</v>
+      </c>
+      <c r="B87" t="s">
         <v>193</v>
       </c>
-      <c r="B87" t="s">
-        <v>194</v>
-      </c>
       <c r="C87" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D87" s="3">
-        <v>46041.333333333299</v>
-      </c>
-      <c r="E87" s="3">
-        <v>46041.708333333299</v>
+        <v>5</v>
+      </c>
+      <c r="D87" s="4">
+        <v>46038.333333333299</v>
+      </c>
+      <c r="E87" s="4">
+        <v>46038.708333333299</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G87" s="3">
-        <v>46041.333333333299</v>
-      </c>
-      <c r="H87" s="3">
-        <v>46041.708333333299</v>
+        <v>14</v>
+      </c>
+      <c r="G87" s="4">
+        <v>46038.333333333299</v>
+      </c>
+      <c r="H87" s="4">
+        <v>46038.708333333299</v>
       </c>
       <c r="I87" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J87" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K87" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="88" spans="1:11">
       <c r="A88" t="s">
+        <v>194</v>
+      </c>
+      <c r="B88" t="s">
         <v>195</v>
       </c>
-      <c r="B88" t="s">
-        <v>196</v>
-      </c>
       <c r="C88" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D88" s="3">
+        <v>5</v>
+      </c>
+      <c r="D88" s="4">
         <v>46038.333333333299</v>
       </c>
-      <c r="E88" s="3">
+      <c r="E88" s="4">
         <v>46038.708333333299</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G88" s="3">
+        <v>14</v>
+      </c>
+      <c r="G88" s="4">
         <v>46038.333333333299</v>
       </c>
-      <c r="H88" s="3">
+      <c r="H88" s="4">
         <v>46038.708333333299</v>
       </c>
       <c r="I88" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J88" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K88" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="89" spans="1:11">
       <c r="A89" t="s">
+        <v>196</v>
+      </c>
+      <c r="B89" t="s">
         <v>197</v>
       </c>
-      <c r="B89" t="s">
-        <v>198</v>
-      </c>
       <c r="C89" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D89" s="3">
-        <v>46038.333333333299</v>
-      </c>
-      <c r="E89" s="3">
-        <v>46038.708333333299</v>
+        <v>5</v>
+      </c>
+      <c r="D89" s="4">
+        <v>46036.333333333299</v>
+      </c>
+      <c r="E89" s="4">
+        <v>46036.708333333299</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G89" s="3">
-        <v>46038.333333333299</v>
-      </c>
-      <c r="H89" s="3">
-        <v>46038.708333333299</v>
+        <v>14</v>
+      </c>
+      <c r="G89" s="4">
+        <v>46036.333333333299</v>
+      </c>
+      <c r="H89" s="4">
+        <v>46036.708333333299</v>
       </c>
       <c r="I89" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J89" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K89" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="90" spans="1:11">
       <c r="A90" t="s">
+        <v>198</v>
+      </c>
+      <c r="B90" t="s">
         <v>199</v>
       </c>
-      <c r="B90" t="s">
-        <v>200</v>
-      </c>
       <c r="C90" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D90" s="3">
-        <v>46036.333333333299</v>
-      </c>
-      <c r="E90" s="3">
+        <v>5</v>
+      </c>
+      <c r="D90" s="4">
+        <v>46035.333333333299</v>
+      </c>
+      <c r="E90" s="4">
         <v>46036.708333333299</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G90" s="3">
-        <v>46036.333333333299</v>
-      </c>
-      <c r="H90" s="3">
+        <v>14</v>
+      </c>
+      <c r="G90" s="4">
+        <v>46035.333333333299</v>
+      </c>
+      <c r="H90" s="4">
         <v>46036.708333333299</v>
       </c>
       <c r="I90" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J90" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K90" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="91" spans="1:11">
       <c r="A91" t="s">
+        <v>200</v>
+      </c>
+      <c r="B91" t="s">
         <v>201</v>
       </c>
-      <c r="B91" t="s">
-        <v>202</v>
-      </c>
       <c r="C91" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D91" s="3">
+        <v>5</v>
+      </c>
+      <c r="D91" s="4">
         <v>46035.333333333299</v>
       </c>
-      <c r="E91" s="3">
-        <v>46036.708333333299</v>
+      <c r="E91" s="4">
+        <v>46035.708333333299</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G91" s="3">
+        <v>14</v>
+      </c>
+      <c r="G91" s="4">
         <v>46035.333333333299</v>
       </c>
-      <c r="H91" s="3">
-        <v>46036.708333333299</v>
+      <c r="H91" s="4">
+        <v>46035.708333333299</v>
       </c>
       <c r="I91" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J91" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K91" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="92" spans="1:11">
       <c r="A92" t="s">
+        <v>202</v>
+      </c>
+      <c r="B92" t="s">
         <v>203</v>
       </c>
-      <c r="B92" t="s">
-        <v>204</v>
-      </c>
       <c r="C92" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D92" s="3">
-        <v>46035.333333333299</v>
-      </c>
-      <c r="E92" s="3">
-        <v>46035.708333333299</v>
+        <v>5</v>
+      </c>
+      <c r="D92" s="4">
+        <v>46034.333333333299</v>
+      </c>
+      <c r="E92" s="4">
+        <v>46034.708333333299</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G92" s="3">
-        <v>46035.333333333299</v>
-      </c>
-      <c r="H92" s="3">
-        <v>46035.708333333299</v>
+        <v>14</v>
+      </c>
+      <c r="G92" s="4">
+        <v>46034.333333333299</v>
+      </c>
+      <c r="H92" s="4">
+        <v>46034.708333333299</v>
       </c>
       <c r="I92" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J92" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K92" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="93" spans="1:11">
       <c r="A93" t="s">
+        <v>204</v>
+      </c>
+      <c r="B93" t="s">
         <v>205</v>
       </c>
-      <c r="B93" t="s">
-        <v>206</v>
-      </c>
       <c r="C93" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D93" s="3">
-        <v>46034.333333333299</v>
-      </c>
-      <c r="E93" s="3">
-        <v>46034.708333333299</v>
+        <v>5</v>
+      </c>
+      <c r="D93" s="4">
+        <v>46031.333333333299</v>
+      </c>
+      <c r="E93" s="4">
+        <v>46031.708333333299</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G93" s="3">
-        <v>46034.333333333299</v>
-      </c>
-      <c r="H93" s="3">
-        <v>46034.708333333299</v>
+        <v>14</v>
+      </c>
+      <c r="G93" s="4">
+        <v>46031.333333333299</v>
+      </c>
+      <c r="H93" s="4">
+        <v>46031.708333333299</v>
       </c>
       <c r="I93" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J93" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K93" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="94" spans="1:11">
       <c r="A94" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B94" t="s">
-        <v>208</v>
+        <v>69</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D94" s="3">
-        <v>46031.333333333299</v>
-      </c>
-      <c r="E94" s="3">
-        <v>46031.708333333299</v>
+        <v>5</v>
+      </c>
+      <c r="D94" s="4">
+        <v>46029.333333333299</v>
+      </c>
+      <c r="E94" s="4">
+        <v>46041.708333333299</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G94" s="3">
-        <v>46031.333333333299</v>
-      </c>
-      <c r="H94" s="3">
-        <v>46031.708333333299</v>
+        <v>14</v>
+      </c>
+      <c r="G94" s="4">
+        <v>46029.333333333299</v>
+      </c>
+      <c r="H94" s="4">
+        <v>46041.708333333299</v>
       </c>
       <c r="I94" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J94" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K94" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="95" spans="1:11">
       <c r="A95" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B95" t="s">
-        <v>72</v>
+        <v>208</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D95" s="3">
+        <v>5</v>
+      </c>
+      <c r="D95" s="4">
         <v>46029.333333333299</v>
       </c>
-      <c r="E95" s="3">
-        <v>46041.708333333299</v>
+      <c r="E95" s="4">
+        <v>46030.708333333299</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G95" s="3">
+        <v>14</v>
+      </c>
+      <c r="G95" s="4">
         <v>46029.333333333299</v>
       </c>
-      <c r="H95" s="3">
-        <v>46041.708333333299</v>
+      <c r="H95" s="4">
+        <v>46030.708333333299</v>
       </c>
       <c r="I95" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J95" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K95" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="96" spans="1:11">
       <c r="A96" t="s">
+        <v>209</v>
+      </c>
+      <c r="B96" t="s">
         <v>210</v>
       </c>
-      <c r="B96" t="s">
-        <v>211</v>
-      </c>
       <c r="C96" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D96" s="3">
-        <v>46029.333333333299</v>
-      </c>
-      <c r="E96" s="3">
-        <v>46030.708333333299</v>
+        <v>5</v>
+      </c>
+      <c r="D96" s="4">
+        <v>45947.333333333299</v>
+      </c>
+      <c r="E96" s="4">
+        <v>45980.708333333299</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G96" s="3">
-        <v>46029.333333333299</v>
-      </c>
-      <c r="H96" s="3">
-        <v>46030.708333333299</v>
+        <v>14</v>
+      </c>
+      <c r="G96" s="4">
+        <v>45947.333333333299</v>
+      </c>
+      <c r="H96" s="4">
+        <v>45980.708333333299</v>
       </c>
       <c r="I96" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J96" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K96" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="97" spans="1:11">
-      <c r="A97" t="s">
-        <v>212</v>
-      </c>
-      <c r="B97" t="s">
-        <v>213</v>
-      </c>
-      <c r="C97" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D97" s="3">
-        <v>45947.333333333299</v>
-      </c>
-      <c r="E97" s="3">
-        <v>45980.708333333299</v>
-      </c>
-      <c r="F97" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G97" s="3">
-        <v>45947.333333333299</v>
-      </c>
-      <c r="H97" s="3">
-        <v>45980.708333333299</v>
-      </c>
-      <c r="I97" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="J97" t="s">
-        <v>7</v>
-      </c>
-      <c r="K97" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
